--- a/frontend/app testing/selenium_results.xlsx
+++ b/frontend/app testing/selenium_results.xlsx
@@ -617,12 +617,12 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>131.19</v>
+        <v>273.31</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>161.58</v>
+        <v>132.09</v>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>126.63</v>
+        <v>106.08</v>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -725,12 +725,12 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>91.34999999999999</v>
+        <v>189.37</v>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>307.3</v>
+        <v>86.66</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>134.62</v>
+        <v>139.26</v>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>188.49</v>
+        <v>265.12</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>305.48</v>
+        <v>53.1</v>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>234.43</v>
+        <v>192.11</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>133.98</v>
+        <v>313.04</v>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>228.19</v>
+        <v>59.53</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>53.68</v>
+        <v>104.66</v>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>73.45</v>
+        <v>146.39</v>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>69.69</v>
+        <v>195.35</v>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>119.38</v>
+        <v>222.54</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>270.61</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>246.32</v>
+        <v>264.87</v>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>132.51</v>
+        <v>271.57</v>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>114.21</v>
+        <v>303.66</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>247.22</v>
+        <v>206.31</v>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>284.7</v>
+        <v>259.91</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>311.69</v>
+        <v>49.61</v>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>299.32</v>
+        <v>236.83</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>141.56</v>
+        <v>253.19</v>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>305.59</v>
+        <v>253.46</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>231.03</v>
+        <v>260.48</v>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>296.64</v>
+        <v>116.05</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>114.36</v>
+        <v>301.32</v>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>103.33</v>
+        <v>123.15</v>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>141.06</v>
+        <v>76.08</v>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>134.26</v>
+        <v>51.33</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>287.28</v>
+        <v>284.11</v>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>240.1</v>
+        <v>159.57</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>236.17</v>
+        <v>105.25</v>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>311.12</v>
+        <v>96.5</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1877,12 +1877,12 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>278.42</v>
+        <v>86.23</v>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>183.29</v>
+        <v>153.42</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>160.86</v>
+        <v>216.89</v>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>93.51000000000001</v>
+        <v>182.57</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>51.33</v>
+        <v>127.91</v>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2057,12 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>122.07</v>
+        <v>163.96</v>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>282.34</v>
+        <v>51.09</v>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>67.78</v>
+        <v>55.63</v>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2165,12 +2165,12 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>272.99</v>
+        <v>259.52</v>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>204.31</v>
+        <v>292.97</v>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2237,12 +2237,12 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>62.97</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2273,12 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>218.72</v>
+        <v>218.68</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>203.12</v>
+        <v>155.53</v>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2345,12 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>89.03</v>
+        <v>260.13</v>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>238.87</v>
+        <v>128.75</v>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>304.99</v>
+        <v>132.79</v>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2453,12 +2453,12 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>53.15</v>
+        <v>93.69</v>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2489,12 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>132.98</v>
+        <v>116.34</v>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>306.61</v>
+        <v>231.47</v>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>64.12</v>
+        <v>51.56</v>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2597,12 +2597,12 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>252.77</v>
+        <v>268.01</v>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2633,12 +2633,12 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>246.63</v>
+        <v>228.21</v>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>305.75</v>
+        <v>237.39</v>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2705,12 +2705,12 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>179.19</v>
+        <v>130.52</v>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2741,12 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>56.75</v>
+        <v>171.2</v>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>163</v>
+        <v>192.66</v>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2813,12 +2813,12 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>166.57</v>
+        <v>287.24</v>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>189.05</v>
+        <v>278.22</v>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>89.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2921,12 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>75.89</v>
+        <v>253.57</v>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2957,12 +2957,12 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>105.38</v>
+        <v>236.86</v>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>186.33</v>
+        <v>100.47</v>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>156.65</v>
+        <v>183.56</v>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3065,12 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>164.07</v>
+        <v>220.97</v>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3101,12 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>315.75</v>
+        <v>128.96</v>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>191.14</v>
+        <v>252.24</v>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3173,12 +3173,12 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>88.88</v>
+        <v>137.19</v>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3209,12 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>160.18</v>
+        <v>231.78</v>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>195.41</v>
+        <v>152.57</v>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3281,12 +3281,12 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>177.13</v>
+        <v>317.57</v>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>156.69</v>
+        <v>315.51</v>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>257.23</v>
+        <v>177.84</v>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>58.27</v>
+        <v>267.86</v>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3425,12 +3425,12 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>252.72</v>
+        <v>125.03</v>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>252.64</v>
+        <v>317.11</v>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3497,12 +3497,12 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>121.52</v>
+        <v>183.57</v>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3533,12 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>186.42</v>
+        <v>187.26</v>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>139.9</v>
+        <v>274.72</v>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3605,12 +3605,12 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>302.7</v>
+        <v>198.29</v>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3641,12 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>309.88</v>
+        <v>238.79</v>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3677,12 +3677,12 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>242.88</v>
+        <v>47.82</v>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3713,12 +3713,12 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>313.1</v>
+        <v>191.97</v>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>133.6</v>
+        <v>150.31</v>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>223.04</v>
+        <v>279.25</v>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>104.17</v>
+        <v>259.4</v>
       </c>
       <c r="G91" s="4" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3857,12 +3857,12 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>298.73</v>
+        <v>300.77</v>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>166.13</v>
+        <v>193.64</v>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>253.14</v>
+        <v>136.42</v>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3965,12 +3965,12 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>78.14</v>
+        <v>73.62</v>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>134.31</v>
+        <v>90.66</v>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>80.45</v>
+        <v>174.83</v>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4073,12 +4073,12 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>319.21</v>
+        <v>97.14</v>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>212.33</v>
+        <v>212.53</v>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>56.6</v>
+        <v>136.18</v>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>114.33</v>
+        <v>230.32</v>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4217,12 +4217,12 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>126.42</v>
+        <v>285.93</v>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>211.07</v>
+        <v>250.49</v>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4289,12 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>75.26000000000001</v>
+        <v>174.92</v>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4325,12 +4325,12 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>313.03</v>
+        <v>270.74</v>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4361,12 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>251.62</v>
+        <v>98.59</v>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>279.11</v>
+        <v>318.83</v>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4433,12 +4433,12 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>194.26</v>
+        <v>319.92</v>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>89.83</v>
+        <v>52.45</v>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4505,12 +4505,12 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>222.78</v>
+        <v>218.06</v>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>201.04</v>
+        <v>123.65</v>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4577,12 +4577,12 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>306.64</v>
+        <v>246.56</v>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>275.4</v>
+        <v>236.86</v>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>208.26</v>
+        <v>75.42</v>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4685,12 +4685,12 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>258.35</v>
+        <v>82.13</v>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4721,12 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>130.95</v>
+        <v>206.35</v>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4757,12 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>245.98</v>
+        <v>288.17</v>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4793,12 +4793,12 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>91.83</v>
+        <v>251.48</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>113.15</v>
+        <v>170.61</v>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4865,12 +4865,12 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>224.41</v>
+        <v>316.24</v>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4901,12 +4901,12 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>67.04000000000001</v>
+        <v>179.51</v>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>159.51</v>
+        <v>185.15</v>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4973,12 +4973,12 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>168.92</v>
+        <v>264.61</v>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5009,12 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>158.35</v>
+        <v>173.85</v>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5045,12 +5045,12 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>156.02</v>
+        <v>291.35</v>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>214.83</v>
+        <v>270.51</v>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5117,12 +5117,12 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>283.35</v>
+        <v>186.95</v>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5153,12 +5153,12 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>64.84</v>
+        <v>279.63</v>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>206.42</v>
+        <v>108.86</v>
       </c>
       <c r="G129" s="4" t="inlineStr"/>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5225,12 +5225,12 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>128.72</v>
+        <v>179.08</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5261,12 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>285.81</v>
+        <v>64.52</v>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>114.87</v>
+        <v>69.52</v>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5333,12 +5333,12 @@
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>185.37</v>
+        <v>232.16</v>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>207.43</v>
+        <v>168.01</v>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5405,12 +5405,12 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>230.83</v>
+        <v>283.67</v>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5441,12 +5441,12 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>304.14</v>
+        <v>205.11</v>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5477,12 +5477,12 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>249.85</v>
+        <v>146.1</v>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5513,12 +5513,12 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>119.13</v>
+        <v>132.52</v>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5549,12 +5549,12 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>93.56999999999999</v>
+        <v>96.95</v>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5585,12 +5585,12 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>237.4</v>
+        <v>270.84</v>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>281.99</v>
+        <v>63.95</v>
       </c>
       <c r="G141" s="4" t="inlineStr"/>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5657,12 +5657,12 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>93.84999999999999</v>
+        <v>314.13</v>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5693,12 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>183.16</v>
+        <v>73.25</v>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>193.93</v>
+        <v>136.47</v>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5765,12 +5765,12 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>124.7</v>
+        <v>227.13</v>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5801,12 +5801,12 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>148.48</v>
+        <v>188.54</v>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5837,12 +5837,12 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>209.05</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5873,12 +5873,12 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>209.76</v>
+        <v>268.94</v>
       </c>
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>293.7</v>
+        <v>212.23</v>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5945,12 +5945,12 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>286.93</v>
+        <v>300.49</v>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>81.45999999999999</v>
+        <v>195.36</v>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6017,12 +6017,12 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>191.28</v>
+        <v>185.73</v>
       </c>
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6053,12 @@
         </is>
       </c>
       <c r="F153" s="4" t="n">
-        <v>153.38</v>
+        <v>191.61</v>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>240.24</v>
+        <v>155.09</v>
       </c>
       <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6125,12 +6125,12 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>86.31</v>
+        <v>56.08</v>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6161,12 +6161,12 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>81.54000000000001</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6197,12 +6197,12 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>298.31</v>
+        <v>172.31</v>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6233,12 +6233,12 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>112.34</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6269,12 +6269,12 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>317.64</v>
+        <v>296.46</v>
       </c>
       <c r="G159" s="4" t="inlineStr"/>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>247.45</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>249.18</v>
+        <v>128.48</v>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6377,12 +6377,12 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>150.08</v>
+        <v>117.61</v>
       </c>
       <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>82.79000000000001</v>
+        <v>265.24</v>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>108.58</v>
+        <v>304.82</v>
       </c>
       <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6485,12 +6485,12 @@
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>217.74</v>
+        <v>46.1</v>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>287.41</v>
+        <v>286.76</v>
       </c>
       <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6557,12 +6557,12 @@
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>284</v>
+        <v>292.44</v>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6593,12 +6593,12 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>218.26</v>
+        <v>231.61</v>
       </c>
       <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>57.62</v>
+        <v>163.63</v>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>272.54</v>
+        <v>204.99</v>
       </c>
       <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>187.53</v>
+        <v>200.26</v>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6737,12 +6737,12 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>143.83</v>
+        <v>138.76</v>
       </c>
       <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6773,12 +6773,12 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>274.47</v>
+        <v>229.38</v>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>107.93</v>
+        <v>319.88</v>
       </c>
       <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6845,12 +6845,12 @@
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>72.31999999999999</v>
+        <v>248.88</v>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6881,12 +6881,12 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>305.93</v>
+        <v>56.35</v>
       </c>
       <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>249.66</v>
+        <v>64.27</v>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6953,12 +6953,12 @@
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>109.15</v>
+        <v>164.01</v>
       </c>
       <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>103.46</v>
+        <v>319.81</v>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7025,12 +7025,12 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>49.91</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7061,12 +7061,12 @@
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>261.99</v>
+        <v>159.92</v>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7097,12 +7097,12 @@
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>136.4</v>
+        <v>278.88</v>
       </c>
       <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7133,12 +7133,12 @@
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>168.4</v>
+        <v>180.58</v>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7169,12 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>311.46</v>
+        <v>192.63</v>
       </c>
       <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7205,12 +7205,12 @@
         </is>
       </c>
       <c r="F185" s="4" t="n">
-        <v>150.51</v>
+        <v>179.24</v>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7241,12 +7241,12 @@
         </is>
       </c>
       <c r="F186" s="2" t="n">
-        <v>82.81999999999999</v>
+        <v>256.35</v>
       </c>
       <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7277,12 +7277,12 @@
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>261.84</v>
+        <v>279.78</v>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7313,12 +7313,12 @@
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>155.72</v>
+        <v>163.7</v>
       </c>
       <c r="G188" s="2" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
         </is>
       </c>
       <c r="F189" s="4" t="n">
-        <v>184.84</v>
+        <v>300.34</v>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7385,12 +7385,12 @@
         </is>
       </c>
       <c r="F190" s="2" t="n">
-        <v>194.49</v>
+        <v>132.14</v>
       </c>
       <c r="G190" s="2" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7421,12 +7421,12 @@
         </is>
       </c>
       <c r="F191" s="4" t="n">
-        <v>294.05</v>
+        <v>116.83</v>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7457,12 +7457,12 @@
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>305.57</v>
+        <v>265.69</v>
       </c>
       <c r="G192" s="2" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7493,12 +7493,12 @@
         </is>
       </c>
       <c r="F193" s="4" t="n">
-        <v>105.91</v>
+        <v>170.82</v>
       </c>
       <c r="G193" s="4" t="inlineStr"/>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>219.94</v>
+        <v>122.91</v>
       </c>
       <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
         </is>
       </c>
       <c r="F195" s="4" t="n">
-        <v>165.25</v>
+        <v>204.1</v>
       </c>
       <c r="G195" s="4" t="inlineStr"/>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7601,12 +7601,12 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>151.79</v>
+        <v>103.59</v>
       </c>
       <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
         </is>
       </c>
       <c r="F197" s="4" t="n">
-        <v>185.78</v>
+        <v>84.3</v>
       </c>
       <c r="G197" s="4" t="inlineStr"/>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7673,12 +7673,12 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>55.6</v>
+        <v>178.89</v>
       </c>
       <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7709,12 +7709,12 @@
         </is>
       </c>
       <c r="F199" s="4" t="n">
-        <v>188.47</v>
+        <v>92.88</v>
       </c>
       <c r="G199" s="4" t="inlineStr"/>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7745,12 +7745,12 @@
         </is>
       </c>
       <c r="F200" s="2" t="n">
-        <v>57.4</v>
+        <v>213.03</v>
       </c>
       <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>155.24</v>
+        <v>294.97</v>
       </c>
       <c r="G201" s="4" t="inlineStr"/>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7817,12 +7817,12 @@
         </is>
       </c>
       <c r="F202" s="2" t="n">
-        <v>148.89</v>
+        <v>91.06</v>
       </c>
       <c r="G202" s="2" t="inlineStr"/>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7853,12 +7853,12 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>182.01</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="G203" s="4" t="inlineStr"/>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
         </is>
       </c>
       <c r="F204" s="2" t="n">
-        <v>256.86</v>
+        <v>213.02</v>
       </c>
       <c r="G204" s="2" t="inlineStr"/>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7925,12 +7925,12 @@
         </is>
       </c>
       <c r="F205" s="4" t="n">
-        <v>267.75</v>
+        <v>312.51</v>
       </c>
       <c r="G205" s="4" t="inlineStr"/>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7961,12 +7961,12 @@
         </is>
       </c>
       <c r="F206" s="2" t="n">
-        <v>152.26</v>
+        <v>266.04</v>
       </c>
       <c r="G206" s="2" t="inlineStr"/>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7997,12 +7997,12 @@
         </is>
       </c>
       <c r="F207" s="4" t="n">
-        <v>233.17</v>
+        <v>63.02</v>
       </c>
       <c r="G207" s="4" t="inlineStr"/>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>194.07</v>
+        <v>217.45</v>
       </c>
       <c r="G208" s="2" t="inlineStr"/>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8069,12 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>209.31</v>
+        <v>233.04</v>
       </c>
       <c r="G209" s="4" t="inlineStr"/>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8105,12 +8105,12 @@
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>131.31</v>
+        <v>251.15</v>
       </c>
       <c r="G210" s="2" t="inlineStr"/>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8141,12 +8141,12 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>300.02</v>
+        <v>174.68</v>
       </c>
       <c r="G211" s="4" t="inlineStr"/>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
         </is>
       </c>
       <c r="F212" s="2" t="n">
-        <v>209.49</v>
+        <v>273.26</v>
       </c>
       <c r="G212" s="2" t="inlineStr"/>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8213,12 +8213,12 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>214.45</v>
+        <v>281.86</v>
       </c>
       <c r="G213" s="4" t="inlineStr"/>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>265.04</v>
+        <v>244.72</v>
       </c>
       <c r="G214" s="2" t="inlineStr"/>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8285,12 +8285,12 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>266.45</v>
+        <v>279.04</v>
       </c>
       <c r="G215" s="4" t="inlineStr"/>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8321,12 @@
         </is>
       </c>
       <c r="F216" s="2" t="n">
-        <v>84.41</v>
+        <v>213.02</v>
       </c>
       <c r="G216" s="2" t="inlineStr"/>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8357,12 +8357,12 @@
         </is>
       </c>
       <c r="F217" s="4" t="n">
-        <v>130.3</v>
+        <v>266.99</v>
       </c>
       <c r="G217" s="4" t="inlineStr"/>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8393,12 +8393,12 @@
         </is>
       </c>
       <c r="F218" s="2" t="n">
-        <v>136.15</v>
+        <v>45.11</v>
       </c>
       <c r="G218" s="2" t="inlineStr"/>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8429,12 @@
         </is>
       </c>
       <c r="F219" s="4" t="n">
-        <v>234.36</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="G219" s="4" t="inlineStr"/>
       <c r="H219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8465,12 +8465,12 @@
         </is>
       </c>
       <c r="F220" s="2" t="n">
-        <v>228.94</v>
+        <v>110.93</v>
       </c>
       <c r="G220" s="2" t="inlineStr"/>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8501,12 +8501,12 @@
         </is>
       </c>
       <c r="F221" s="4" t="n">
-        <v>278.33</v>
+        <v>200.35</v>
       </c>
       <c r="G221" s="4" t="inlineStr"/>
       <c r="H221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8537,12 +8537,12 @@
         </is>
       </c>
       <c r="F222" s="2" t="n">
-        <v>130.35</v>
+        <v>98</v>
       </c>
       <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8573,12 +8573,12 @@
         </is>
       </c>
       <c r="F223" s="4" t="n">
-        <v>296.92</v>
+        <v>169.12</v>
       </c>
       <c r="G223" s="4" t="inlineStr"/>
       <c r="H223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
         </is>
       </c>
       <c r="F224" s="2" t="n">
-        <v>292.42</v>
+        <v>105.33</v>
       </c>
       <c r="G224" s="2" t="inlineStr"/>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8645,12 +8645,12 @@
         </is>
       </c>
       <c r="F225" s="4" t="n">
-        <v>274.24</v>
+        <v>199.82</v>
       </c>
       <c r="G225" s="4" t="inlineStr"/>
       <c r="H225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8681,12 +8681,12 @@
         </is>
       </c>
       <c r="F226" s="2" t="n">
-        <v>101.47</v>
+        <v>274.04</v>
       </c>
       <c r="G226" s="2" t="inlineStr"/>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8717,12 @@
         </is>
       </c>
       <c r="F227" s="4" t="n">
-        <v>149.13</v>
+        <v>56.57</v>
       </c>
       <c r="G227" s="4" t="inlineStr"/>
       <c r="H227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8753,12 +8753,12 @@
         </is>
       </c>
       <c r="F228" s="2" t="n">
-        <v>56.28</v>
+        <v>184</v>
       </c>
       <c r="G228" s="2" t="inlineStr"/>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
         </is>
       </c>
       <c r="F229" s="4" t="n">
-        <v>81.8</v>
+        <v>220.21</v>
       </c>
       <c r="G229" s="4" t="inlineStr"/>
       <c r="H229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8825,12 +8825,12 @@
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>244.26</v>
+        <v>132.65</v>
       </c>
       <c r="G230" s="2" t="inlineStr"/>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
         </is>
       </c>
       <c r="F231" s="4" t="n">
-        <v>65.91</v>
+        <v>145.89</v>
       </c>
       <c r="G231" s="4" t="inlineStr"/>
       <c r="H231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8897,12 +8897,12 @@
         </is>
       </c>
       <c r="F232" s="2" t="n">
-        <v>114.29</v>
+        <v>81.3</v>
       </c>
       <c r="G232" s="2" t="inlineStr"/>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
         </is>
       </c>
       <c r="F233" s="4" t="n">
-        <v>121.69</v>
+        <v>190.65</v>
       </c>
       <c r="G233" s="4" t="inlineStr"/>
       <c r="H233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8969,12 +8969,12 @@
         </is>
       </c>
       <c r="F234" s="2" t="n">
-        <v>276.92</v>
+        <v>209.03</v>
       </c>
       <c r="G234" s="2" t="inlineStr"/>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9005,12 +9005,12 @@
         </is>
       </c>
       <c r="F235" s="4" t="n">
-        <v>140.1</v>
+        <v>150.66</v>
       </c>
       <c r="G235" s="4" t="inlineStr"/>
       <c r="H235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9041,12 +9041,12 @@
         </is>
       </c>
       <c r="F236" s="2" t="n">
-        <v>274.93</v>
+        <v>225.18</v>
       </c>
       <c r="G236" s="2" t="inlineStr"/>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9077,12 +9077,12 @@
         </is>
       </c>
       <c r="F237" s="4" t="n">
-        <v>136.73</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="G237" s="4" t="inlineStr"/>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9113,12 +9113,12 @@
         </is>
       </c>
       <c r="F238" s="2" t="n">
-        <v>206.72</v>
+        <v>182.81</v>
       </c>
       <c r="G238" s="2" t="inlineStr"/>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
         </is>
       </c>
       <c r="F239" s="4" t="n">
-        <v>311.57</v>
+        <v>96.3</v>
       </c>
       <c r="G239" s="4" t="inlineStr"/>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9185,12 +9185,12 @@
         </is>
       </c>
       <c r="F240" s="2" t="n">
-        <v>57.2</v>
+        <v>83.37</v>
       </c>
       <c r="G240" s="2" t="inlineStr"/>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9221,12 +9221,12 @@
         </is>
       </c>
       <c r="F241" s="4" t="n">
-        <v>164.29</v>
+        <v>89.34</v>
       </c>
       <c r="G241" s="4" t="inlineStr"/>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9257,12 +9257,12 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>151.99</v>
+        <v>78.22</v>
       </c>
       <c r="G242" s="2" t="inlineStr"/>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9293,12 +9293,12 @@
         </is>
       </c>
       <c r="F243" s="4" t="n">
-        <v>236.82</v>
+        <v>157.76</v>
       </c>
       <c r="G243" s="4" t="inlineStr"/>
       <c r="H243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9329,12 +9329,12 @@
         </is>
       </c>
       <c r="F244" s="2" t="n">
-        <v>166.39</v>
+        <v>297.16</v>
       </c>
       <c r="G244" s="2" t="inlineStr"/>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9365,12 +9365,12 @@
         </is>
       </c>
       <c r="F245" s="4" t="n">
-        <v>56.97</v>
+        <v>91.88</v>
       </c>
       <c r="G245" s="4" t="inlineStr"/>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9401,12 +9401,12 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>192.43</v>
+        <v>142.56</v>
       </c>
       <c r="G246" s="2" t="inlineStr"/>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
         </is>
       </c>
       <c r="F247" s="4" t="n">
-        <v>108.15</v>
+        <v>241.16</v>
       </c>
       <c r="G247" s="4" t="inlineStr"/>
       <c r="H247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9473,12 +9473,12 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>188.33</v>
+        <v>154.94</v>
       </c>
       <c r="G248" s="2" t="inlineStr"/>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9509,12 +9509,12 @@
         </is>
       </c>
       <c r="F249" s="4" t="n">
-        <v>218.49</v>
+        <v>208.32</v>
       </c>
       <c r="G249" s="4" t="inlineStr"/>
       <c r="H249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9545,12 +9545,12 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>126.22</v>
+        <v>197.87</v>
       </c>
       <c r="G250" s="2" t="inlineStr"/>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9581,12 +9581,12 @@
         </is>
       </c>
       <c r="F251" s="4" t="n">
-        <v>206.32</v>
+        <v>302.58</v>
       </c>
       <c r="G251" s="4" t="inlineStr"/>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9617,12 +9617,12 @@
         </is>
       </c>
       <c r="F252" s="2" t="n">
-        <v>103.07</v>
+        <v>67.45</v>
       </c>
       <c r="G252" s="2" t="inlineStr"/>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9653,12 +9653,12 @@
         </is>
       </c>
       <c r="F253" s="4" t="n">
-        <v>299.68</v>
+        <v>279.6</v>
       </c>
       <c r="G253" s="4" t="inlineStr"/>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9689,12 +9689,12 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>293.15</v>
+        <v>58.08</v>
       </c>
       <c r="G254" s="2" t="inlineStr"/>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9725,12 +9725,12 @@
         </is>
       </c>
       <c r="F255" s="4" t="n">
-        <v>80.26000000000001</v>
+        <v>251.21</v>
       </c>
       <c r="G255" s="4" t="inlineStr"/>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9761,12 +9761,12 @@
         </is>
       </c>
       <c r="F256" s="2" t="n">
-        <v>251.25</v>
+        <v>260.07</v>
       </c>
       <c r="G256" s="2" t="inlineStr"/>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9797,12 +9797,12 @@
         </is>
       </c>
       <c r="F257" s="4" t="n">
-        <v>288.89</v>
+        <v>243.44</v>
       </c>
       <c r="G257" s="4" t="inlineStr"/>
       <c r="H257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>207.25</v>
+        <v>306.72</v>
       </c>
       <c r="G258" s="2" t="inlineStr"/>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
         </is>
       </c>
       <c r="F259" s="4" t="n">
-        <v>77.88</v>
+        <v>170.36</v>
       </c>
       <c r="G259" s="4" t="inlineStr"/>
       <c r="H259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9905,12 +9905,12 @@
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>266.99</v>
+        <v>281.55</v>
       </c>
       <c r="G260" s="2" t="inlineStr"/>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9941,12 +9941,12 @@
         </is>
       </c>
       <c r="F261" s="4" t="n">
-        <v>217.45</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="G261" s="4" t="inlineStr"/>
       <c r="H261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>113.37</v>
+        <v>173.23</v>
       </c>
       <c r="G262" s="2" t="inlineStr"/>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
         </is>
       </c>
       <c r="F263" s="4" t="n">
-        <v>282.45</v>
+        <v>176.8</v>
       </c>
       <c r="G263" s="4" t="inlineStr"/>
       <c r="H263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10049,12 +10049,12 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>83.05</v>
+        <v>260.32</v>
       </c>
       <c r="G264" s="2" t="inlineStr"/>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10085,12 +10085,12 @@
         </is>
       </c>
       <c r="F265" s="4" t="n">
-        <v>109.72</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="G265" s="4" t="inlineStr"/>
       <c r="H265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10121,12 +10121,12 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>57.91</v>
+        <v>111.8</v>
       </c>
       <c r="G266" s="2" t="inlineStr"/>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10157,12 +10157,12 @@
         </is>
       </c>
       <c r="F267" s="4" t="n">
-        <v>167.59</v>
+        <v>119.54</v>
       </c>
       <c r="G267" s="4" t="inlineStr"/>
       <c r="H267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10193,12 +10193,12 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>178.09</v>
+        <v>53.1</v>
       </c>
       <c r="G268" s="2" t="inlineStr"/>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10229,12 +10229,12 @@
         </is>
       </c>
       <c r="F269" s="4" t="n">
-        <v>306.08</v>
+        <v>85.61</v>
       </c>
       <c r="G269" s="4" t="inlineStr"/>
       <c r="H269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10265,12 +10265,12 @@
         </is>
       </c>
       <c r="F270" s="2" t="n">
-        <v>97.17</v>
+        <v>316.33</v>
       </c>
       <c r="G270" s="2" t="inlineStr"/>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10301,12 +10301,12 @@
         </is>
       </c>
       <c r="F271" s="4" t="n">
-        <v>132.5</v>
+        <v>206.01</v>
       </c>
       <c r="G271" s="4" t="inlineStr"/>
       <c r="H271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10337,12 +10337,12 @@
         </is>
       </c>
       <c r="F272" s="2" t="n">
-        <v>290.07</v>
+        <v>130.28</v>
       </c>
       <c r="G272" s="2" t="inlineStr"/>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10373,12 +10373,12 @@
         </is>
       </c>
       <c r="F273" s="4" t="n">
-        <v>77.77</v>
+        <v>269.51</v>
       </c>
       <c r="G273" s="4" t="inlineStr"/>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10409,12 +10409,12 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>305.52</v>
+        <v>179.05</v>
       </c>
       <c r="G274" s="2" t="inlineStr"/>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10445,12 +10445,12 @@
         </is>
       </c>
       <c r="F275" s="4" t="n">
-        <v>81.69</v>
+        <v>69.64</v>
       </c>
       <c r="G275" s="4" t="inlineStr"/>
       <c r="H275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10481,12 +10481,12 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>94.73</v>
+        <v>213.99</v>
       </c>
       <c r="G276" s="2" t="inlineStr"/>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10517,12 +10517,12 @@
         </is>
       </c>
       <c r="F277" s="4" t="n">
-        <v>292.02</v>
+        <v>178.53</v>
       </c>
       <c r="G277" s="4" t="inlineStr"/>
       <c r="H277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10553,12 +10553,12 @@
         </is>
       </c>
       <c r="F278" s="2" t="n">
-        <v>301.82</v>
+        <v>267.36</v>
       </c>
       <c r="G278" s="2" t="inlineStr"/>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10589,12 +10589,12 @@
         </is>
       </c>
       <c r="F279" s="4" t="n">
-        <v>196.09</v>
+        <v>256.18</v>
       </c>
       <c r="G279" s="4" t="inlineStr"/>
       <c r="H279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10625,12 +10625,12 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>182.4</v>
+        <v>138.43</v>
       </c>
       <c r="G280" s="2" t="inlineStr"/>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10661,12 +10661,12 @@
         </is>
       </c>
       <c r="F281" s="4" t="n">
-        <v>162.16</v>
+        <v>48.77</v>
       </c>
       <c r="G281" s="4" t="inlineStr"/>
       <c r="H281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10697,12 +10697,12 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>60.15</v>
+        <v>139.98</v>
       </c>
       <c r="G282" s="2" t="inlineStr"/>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10733,12 +10733,12 @@
         </is>
       </c>
       <c r="F283" s="4" t="n">
-        <v>131.18</v>
+        <v>49.43</v>
       </c>
       <c r="G283" s="4" t="inlineStr"/>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10769,12 +10769,12 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>62.52</v>
+        <v>293.98</v>
       </c>
       <c r="G284" s="2" t="inlineStr"/>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10805,12 +10805,12 @@
         </is>
       </c>
       <c r="F285" s="4" t="n">
-        <v>162.92</v>
+        <v>156</v>
       </c>
       <c r="G285" s="4" t="inlineStr"/>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10841,12 +10841,12 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>319.38</v>
+        <v>282.51</v>
       </c>
       <c r="G286" s="2" t="inlineStr"/>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10877,12 +10877,12 @@
         </is>
       </c>
       <c r="F287" s="4" t="n">
-        <v>103.09</v>
+        <v>90.08</v>
       </c>
       <c r="G287" s="4" t="inlineStr"/>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10913,12 +10913,12 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>233.46</v>
+        <v>153.21</v>
       </c>
       <c r="G288" s="2" t="inlineStr"/>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10949,12 +10949,12 @@
         </is>
       </c>
       <c r="F289" s="4" t="n">
-        <v>87.08</v>
+        <v>102.19</v>
       </c>
       <c r="G289" s="4" t="inlineStr"/>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10985,12 +10985,12 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>150.81</v>
+        <v>228.25</v>
       </c>
       <c r="G290" s="2" t="inlineStr"/>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11021,12 +11021,12 @@
         </is>
       </c>
       <c r="F291" s="4" t="n">
-        <v>263.37</v>
+        <v>136.3</v>
       </c>
       <c r="G291" s="4" t="inlineStr"/>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11057,12 +11057,12 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>107.22</v>
+        <v>188.21</v>
       </c>
       <c r="G292" s="2" t="inlineStr"/>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11093,12 +11093,12 @@
         </is>
       </c>
       <c r="F293" s="4" t="n">
-        <v>177.72</v>
+        <v>141.59</v>
       </c>
       <c r="G293" s="4" t="inlineStr"/>
       <c r="H293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11129,12 +11129,12 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>54.28</v>
+        <v>178.38</v>
       </c>
       <c r="G294" s="2" t="inlineStr"/>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11165,12 +11165,12 @@
         </is>
       </c>
       <c r="F295" s="4" t="n">
-        <v>255.7</v>
+        <v>80.75</v>
       </c>
       <c r="G295" s="4" t="inlineStr"/>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11201,12 +11201,12 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>162.38</v>
+        <v>243.77</v>
       </c>
       <c r="G296" s="2" t="inlineStr"/>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
         </is>
       </c>
       <c r="F297" s="4" t="n">
-        <v>293.92</v>
+        <v>295.98</v>
       </c>
       <c r="G297" s="4" t="inlineStr"/>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11273,12 +11273,12 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>93.41</v>
+        <v>137.46</v>
       </c>
       <c r="G298" s="2" t="inlineStr"/>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
         </is>
       </c>
       <c r="F299" s="4" t="n">
-        <v>82.42</v>
+        <v>309.41</v>
       </c>
       <c r="G299" s="4" t="inlineStr"/>
       <c r="H299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11345,12 +11345,12 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>319.02</v>
+        <v>306.08</v>
       </c>
       <c r="G300" s="2" t="inlineStr"/>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11381,12 +11381,12 @@
         </is>
       </c>
       <c r="F301" s="4" t="n">
-        <v>268.2</v>
+        <v>294.22</v>
       </c>
       <c r="G301" s="4" t="inlineStr"/>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:37</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11418,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-01 09:38:37</t>
+          <t>Generated: 2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
